--- a/naver-place-crawler/results_health/군위군_헬스장.xlsx
+++ b/naver-place-crawler/results_health/군위군_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,38 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>엠투피 구평점</t>
+          <t>짐다이나믹</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>m2plove@naver.com</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>m2plove@m2p.co.kr</t>
-        </is>
-      </c>
+          <t>ckdsha77@naver.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1358-9689</t>
+          <t>0507-1319-1733</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경북 구미시 인동38길 5-9</t>
+          <t>경상북도 구미시 인동중앙로3길 14 인동프라자 202호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://www.m2p.co.kr</t>
+          <t>https://www.instagram.com/gym_dynamic</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -605,19 +601,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ij1u</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -629,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>372</v>
+        <v>21</v>
       </c>
       <c r="Q2" t="n">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="R2" t="n">
-        <v>435</v>
+        <v>40</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -644,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1735292694</t>
+          <t>1756168748</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1735292694</t>
+          <t>https://m.place.naver.com/place/1756168748</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -666,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>피트니스247</t>
+          <t>팀JJ피트니스 옥계점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>seop__e@naver.com</t>
+          <t>teamjj0626@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1399-2471</t>
+          <t>0507-1486-8853</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경북 구미시 인동중앙로11길 26 3층 피트니스247</t>
+          <t>경상북도 구미시 옥계북로 22 7층, 6층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fitness247_gumi/</t>
+          <t>https://blog.naver.com/teamjj0626</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -703,19 +695,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4goc4</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -727,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>414</v>
+        <v>1966</v>
       </c>
       <c r="Q3" t="n">
-        <v>284</v>
+        <v>324</v>
       </c>
       <c r="R3" t="n">
-        <v>698</v>
+        <v>2290</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -742,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1579467156</t>
+          <t>1389388394</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1579467156</t>
+          <t>https://m.place.naver.com/place/1389388394</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -764,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>제이원 스파랜드 구미점</t>
+          <t>온리원피트니스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jewel2248@naver.com</t>
+          <t>onlyone_pt@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>054-471-0011</t>
+          <t>0507-1405-6622</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경북 구미시 산동읍 강동로 1159-57</t>
+          <t>경상북도 구미시 인동가산로 35 3층, 4층, 5층 온리원 피트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jone.gumi?igsh=N2l3OTR0MGIyem00&amp;utm_source=ig_contact_invite</t>
+          <t>https://blog.naver.com/onlyone_pt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -801,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -812,7 +800,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>147</v>
+        <v>309</v>
       </c>
       <c r="Q4" t="n">
-        <v>53</v>
+        <v>130</v>
       </c>
       <c r="R4" t="n">
-        <v>200</v>
+        <v>439</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1187212013</t>
+          <t>15864016</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1187212013</t>
+          <t>https://m.place.naver.com/place/15864016</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -858,29 +846,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>팀JJ피트니스 옥계점</t>
+          <t>PT LAB.피트니스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>teamjj0626@naver.com</t>
+          <t>ptlab21@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0507-1486-8853</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경북 구미시 옥계북로 22 7층, 6층</t>
+          <t>경상북도 구미시 옥계북로 34 원광빌딩, 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/teamjj0626</t>
+          <t>https://blog.naver.com/ptlab21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -900,17 +884,13 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w402ke</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -919,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1962</v>
+        <v>44</v>
       </c>
       <c r="Q5" t="n">
-        <v>322</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>2284</v>
+        <v>48</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,51 +914,47 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1389388394</t>
+          <t>1255504991</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1389388394</t>
+          <t>https://m.place.naver.com/place/1255504991</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>지와이피티샵</t>
+          <t>제이디짐 산동점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>lgy6873@naver.com</t>
+          <t>jdgym6606@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1365-8610</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대구 군위군 군위읍 중앙길 72 2층</t>
+          <t>경상북도 구미시 산동읍 신당1로4길 19 3층 제이디짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gypt86</t>
+          <t>https://blog.naver.com/jdgym6606</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,7 +969,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1013,32 +989,4888 @@
         </is>
       </c>
       <c r="P6" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>81</v>
+      </c>
+      <c r="R6" t="n">
+        <v>256</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>1575783414</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1575783414</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>레디PT 피티샵</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>phil2jh@naver.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1403-0083</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>경상북도 칠곡군 석적읍 남율로2길 1 3층</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_ready_pt.studio?igsh=MXhseW92Y3N0cHNqcA==</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>7</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>1760644933</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1760644933</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>아이엔짐</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ingym_ho@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>070-4101-4354</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 인동중앙로1길 18 2,3층 아이엔짐</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>http://blog.naver.com/ingym_ho</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>93</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>1065996176</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1065996176</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>365피트니스 헬스 PT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>gkgkghgh234@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>054-716-2340</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 산호대로29길 8-3 301호</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/365_fitness24</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>46</v>
+      </c>
+      <c r="R9" t="n">
+        <v>73</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1111348451</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1111348451</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>존킴짐</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>johnkimgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1367-1260</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 산동읍 신당1로2길 15 바젤2차 606호</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/johnkimgym</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>15</v>
+      </c>
+      <c r="R10" t="n">
+        <v>17</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1103689398</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1103689398</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>하더짐</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>qkek630@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1800-9978</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 인동중앙로6길 1 3층</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>18</v>
+      </c>
+      <c r="R11" t="n">
+        <v>65</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1197601467</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1197601467</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Life fitness</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>starrude@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1316-4806</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 인동31길 22-17 4층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>http://instagram.com/</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>24</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1788318048</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1788318048</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>엠투피 산동점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>m2plove@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>m2plove@m2p.co.kr</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1314-3508</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 산동읍 신당2로 57</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>http://www.m2p.co.kr</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>260</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>89</v>
+      </c>
+      <c r="R13" t="n">
+        <v>349</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1373982303</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1373982303</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>컴온짐</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>comeon2525@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>054-474-6262</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 인동가산로 23 지하1층</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://m.cafe.naver.com/machogym</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>9</v>
+      </c>
+      <c r="R14" t="n">
+        <v>15</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1914240718</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1914240718</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>휘트니스인앤아웃</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ouihun@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>054-473-9488</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 산동읍 적림1길 7-3</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>http://blog.naver.com/ouihun</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>81</v>
+      </c>
+      <c r="R15" t="n">
+        <v>84</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>37765614</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37765614</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>파워헬스클럽</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>power2963805@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1433-7656</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 산호대로27길 14 2층</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1197556873</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1197556873</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>인동스피닝</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>lee71002091@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 인동중앙로 16 4층 인동스피닝</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/a0139</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>37841949</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37841949</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>네오젠 골프컨디셔닝 스튜디오</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>hangsangharu@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 인동36길 71</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1986933515</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1986933515</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>티나핏</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>loveseung22@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>경상북도 칠곡군 석적읍 장곡길 119 중앙빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tina_fit__</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>267</v>
+      </c>
+      <c r="R19" t="n">
+        <v>267</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1940941739</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1940941739</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>XO 피트니스 24시</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gg123455@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1374-6544</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 인동북길 83 5,6층</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UC5g0GbfBdaQPl5t3gt1mzLw?si=Vo3FSmjrAXF9KdW4</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>14</v>
+      </c>
+      <c r="R20" t="n">
+        <v>59</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1951938661</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1951938661</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>웰라인 휘트니스</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>topten0@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>054-473-7227</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 인동가산로 9-3 노블레스타워 8층 웰라인휘트니스</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>11</v>
+      </c>
+      <c r="R21" t="n">
+        <v>14</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1506954140</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1506954140</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>엠투피 구평점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>m2plove@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>m2plove@m2p.co.kr</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1358-9689</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 인동38길 5-9</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>http://www.m2p.co.kr</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>373</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>65</v>
+      </c>
+      <c r="R22" t="n">
+        <v>438</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1735292694</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1735292694</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>커브스 구평클럽</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>mik6158@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>054-476-1330</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 인동36길 15 구평메디컬센터 6층</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/mik6158</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>37</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>20460818</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20460818</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>인동스포렉스</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>nunmur0604@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>054-472-7161</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 인동중앙로 23-3</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>21799533</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21799533</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>크로스핏매니악</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>minhuisu@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>054-471-7279</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 옥계북로 36 옥계메디칼타워 지하2층</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/crossfitmaniac</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>114</v>
+      </c>
+      <c r="R25" t="n">
+        <v>117</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>36420484</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36420484</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>로드핏 구평점 헬스 PT</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>lordfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1364-3750</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 인동남길 178 6층, 7층, 8층</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lordfit_gupyeong</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>160</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>111</v>
+      </c>
+      <c r="R26" t="n">
+        <v>271</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2082865295</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2082865295</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>스타헬스</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>147048@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>054-475-1383</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 흥안로 18</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>5</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>15523431</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/15523431</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>점핑피트니스</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>chlgpwjd19@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 인동38길 9-8 종합프라자</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1293494349</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1293494349</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>케이투휘트니스헬스클럽</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>topten0@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1403-7552</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 인동26길 43-4 4층</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4</v>
+      </c>
+      <c r="R29" t="n">
+        <v>4</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1903697781</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1903697781</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>팀JJ피트니스 석적점</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>teamjj0626@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1392-9101</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>경상북도 칠곡군 석적읍 유학로 12 3,4층</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>7</v>
+      </c>
+      <c r="R30" t="n">
+        <v>44</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1501991558</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1501991558</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>구미스포츠월드</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>gbnadri@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>054-471-8965</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 인동35길 32</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>108</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>108</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1573436640</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1573436640</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>목욕탕,사우나</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>천호사우나헬스</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>isis0328@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>054-977-5440</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>경상북도 칠곡군 석적읍 북중리11길 23</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>6</v>
+      </c>
+      <c r="R32" t="n">
+        <v>74</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>15510481</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/15510481</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>피트니스247</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>seop__e@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1399-2471</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 인동중앙로11길 26 3층 피트니스247</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fitness247_gumi/</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>417</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>267</v>
+      </c>
+      <c r="R33" t="n">
+        <v>684</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1579467156</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1579467156</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>피트니스G 헬스.PT 석적점</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>fitnessg4422229@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>054-972-2229</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>경상북도 칠곡군 석적읍 유학로 1 401호</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fitness.g_02</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>132</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>37</v>
+      </c>
+      <c r="R34" t="n">
+        <v>169</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1530354048</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1530354048</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>구미필라테스</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>pmhcrow@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>054-475-4477</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 인동36길 6 5층</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/pmhcrow</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>37</v>
+      </c>
+      <c r="R35" t="n">
+        <v>54</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>19460024</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19460024</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>최재원피트니스 구미인동점</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>energy1262@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1439-9698</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 인동북길 43 4F</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/choijaewonfitness</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>15</v>
+      </c>
+      <c r="R36" t="n">
+        <v>27</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1971423118</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1971423118</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>아이엠헬스&amp;휘트니스</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>imtotal@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>경상북도 칠곡군 석적읍 북중리11길 23</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>15510473</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/15510473</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>에스엘짐</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>tankboy486@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1379-0910</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 검성로 103-7 화진금봉 1차 상가 B1</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/tankboy486</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>25</v>
+      </c>
+      <c r="R38" t="n">
+        <v>79</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1798303624</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1798303624</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>바디엔지니어스짐 산동점</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>bodybody01@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 산동읍 신당1로4길 3 에코빌딩 5,6층</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bodyengineersgym_sandong</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>66</v>
+      </c>
+      <c r="R39" t="n">
+        <v>123</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1046159743</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1046159743</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>스크린골프장</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>골프존파크 유학산골프랜드</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>uc6u1nwg@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1450-0754</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>경상북도 칠곡군 석적읍 동중리1길 99 유학산골프랜드</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>7</v>
+      </c>
+      <c r="R40" t="n">
+        <v>18</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1082856757</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1082856757</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>스포츠센터</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>칠곡국민체육센터</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>workout-_-@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>054-971-1400</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>경상북도 칠곡군 왜관읍 석전로7길 58 칠곡국민체육센터</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/workout-_-</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>125</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>80</v>
+      </c>
+      <c r="R41" t="n">
+        <v>205</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>21117079</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21117079</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>토미짐앤스파</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>tomigym@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>054-471-8964</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 인동35길 32 토미짐앤스파</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/tomigym</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>106</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>160</v>
+      </c>
+      <c r="R42" t="n">
+        <v>266</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>38257162</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38257162</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>이지발란스</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>eb2967@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 인동20길 35 3층</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@user-kb4ot3ev4m</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>35346740</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35346740</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>우먼앤짐</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>woman_and_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 산동읍 신당1로2길 13 1동 206호(바젤메디컬프라자)</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/woman_and_gym_gumi_pt/</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>4</v>
+      </c>
+      <c r="R44" t="n">
+        <v>48</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1934228891</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1934228891</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>제이원 스파랜드 구미점</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>sukja7820@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>054-471-0011</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 산동읍 강동로 1159-57</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jone.gumi?igsh=N2l3OTR0MGIyem00&amp;utm_source=ig_contact_invite</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>148</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>53</v>
+      </c>
+      <c r="R45" t="n">
+        <v>201</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1187212013</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1187212013</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>이루핏</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>papepopo0929@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1353-8028</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 옥계북로10길 4 2층</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>320</v>
+      </c>
+      <c r="R46" t="n">
+        <v>322</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1399469071</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1399469071</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>피티타임/PT</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>shs8461@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>경상북도 칠곡군 석적읍 북중리12길 19 ,2층</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/shs8461</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>32</v>
+      </c>
+      <c r="R47" t="n">
+        <v>72</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1168516436</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1168516436</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>클락짐_Clark Gym</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>sungminjin1004@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1359-2673</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>경상북도 칠곡군 석적읍 북중리10길 26 2층(가람타운)</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kyunghoonji</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>5</v>
+      </c>
+      <c r="R48" t="n">
+        <v>20</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1032303624</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1032303624</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>쇠타작PT</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1288xo@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1346-6290</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 산동읍 신당인덕1로3길 3 4층</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/1288xo</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>16</v>
+      </c>
+      <c r="R49" t="n">
+        <v>38</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1393651171</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1393651171</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>짐케이 PT</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>a319314@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1393-9683</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 산동읍 신당2로 29 6층</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/a319314</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>179</v>
+      </c>
+      <c r="R50" t="n">
+        <v>252</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1055349957</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1055349957</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>지와이피티샵</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>topten0@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1365-8610</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>대구광역시 군위군 군위읍 중앙길 72 2층</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gypt86</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
         <v>10</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q51" t="n">
         <v>7</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R51" t="n">
         <v>17</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
         <is>
           <t>1756594082</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1756594082</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>클린바디</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>dogmini1004@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1322-0960</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 옥계남로 76-20</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/kyw8541</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>124</v>
+      </c>
+      <c r="R52" t="n">
+        <v>125</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1876652098</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1876652098</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>루시피트니스</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>lucy_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1395-4181</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 산호대로29길 9 2층</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lucyfitness_gumi</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>3</v>
+      </c>
+      <c r="R53" t="n">
+        <v>45</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1426804590</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1426804590</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>팀레이피트니스 진평1호점</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>nyunyu@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1313-3551</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 인동22길 19 4층 팀레이 피트니스</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/teamray_1st</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>91</v>
+      </c>
+      <c r="R54" t="n">
+        <v>95</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1235167357</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1235167357</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>율핏</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>jueun931022@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1382-1537</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 인동중앙로1길 1 2층 율핏</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>2</v>
+      </c>
+      <c r="R55" t="n">
+        <v>3</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1395755565</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1395755565</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>헤이핏</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>hyelin0716@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 산동읍 신당4로 115 1동 7F 701호</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/__heyfit</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>230</v>
+      </c>
+      <c r="R56" t="n">
+        <v>249</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1584468732</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1584468732</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>전문건설업</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>미끄럼방지 더쎈논슬립</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>hybridnslip@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1661-7930</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>경상북도 구미시 인동35길 50</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>http://www.thessennonslip.com/</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>2</v>
+      </c>
+      <c r="R57" t="n">
+        <v>4</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>36432808</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36432808</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>체육관</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>석적바디핏휘트니스</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>haon8312@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1360-4700</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>경상북도 칠곡군 석적읍 서중리4길 18-18 바디핏 휘트니스</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>28</v>
+      </c>
+      <c r="R58" t="n">
+        <v>28</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1086372676</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1086372676</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/군위군_헬스장.xlsx
+++ b/naver-place-crawler/results_health/군위군_헬스장.xlsx
@@ -423,7 +423,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>짐다이나믹</t>
+          <t>최재원피트니스 구미인동점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ckdsha77@naver.com</t>
+          <t>energy1262@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1319-1733</t>
+          <t>0507-1439-9698</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동중앙로3길 14 인동프라자 202호</t>
+          <t>경상북도 구미시 인동북길 43 4F</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gym_dynamic</t>
+          <t>https://www.instagram.com/choijaewonfitness</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="R2" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1756168748</t>
+          <t>1971423118</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1756168748</t>
+          <t>https://m.place.naver.com/place/1971423118</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>팀JJ피트니스 옥계점</t>
+          <t>휘트니스인앤아웃</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>teamjj0626@naver.com</t>
+          <t>ouihun@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1486-8853</t>
+          <t>054-473-9488</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계북로 22 7층, 6층</t>
+          <t>경상북도 구미시 산동읍 적림1길 7-3</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/teamjj0626</t>
+          <t>http://blog.naver.com/ouihun</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1966</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="R3" t="n">
-        <v>2290</v>
+        <v>84</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1389388394</t>
+          <t>37765614</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1389388394</t>
+          <t>https://m.place.naver.com/place/37765614</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>온리원피트니스</t>
+          <t>팀JJ피트니스 석적점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>onlyone_pt@naver.com</t>
+          <t>teamjj0626@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1405-6622</t>
+          <t>0507-1392-9101</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동가산로 35 3층, 4층, 5층 온리원 피트니스</t>
+          <t>경상북도 칠곡군 석적읍 유학로 12 3,4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/onlyone_pt</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,12 +784,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -800,22 +800,22 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>309</v>
+        <v>37</v>
       </c>
       <c r="Q4" t="n">
-        <v>130</v>
+        <v>7</v>
       </c>
       <c r="R4" t="n">
-        <v>439</v>
+        <v>44</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>15864016</t>
+          <t>1501991558</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/15864016</t>
+          <t>https://m.place.naver.com/place/1501991558</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -846,25 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PT LAB.피트니스</t>
+          <t>하더짐</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ptlab21@naver.com</t>
+          <t>qkek630@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1800-9978</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계북로 34 원광빌딩, 4층</t>
+          <t>경상북도 구미시 인동중앙로6길 1 3층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ptlab21</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -874,12 +878,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -890,22 +894,22 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="R5" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1255504991</t>
+          <t>1197601467</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1255504991</t>
+          <t>https://m.place.naver.com/place/1197601467</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -936,25 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>제이디짐 산동점</t>
+          <t>웰라인 휘트니스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>jdgym6606@naver.com</t>
+          <t>red_gg0_ma@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>054-473-7227</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로4길 19 3층 제이디짐</t>
+          <t>경상북도 구미시 인동가산로 9-3 노블레스타워 8층 웰라인휘트니스</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jdgym6606</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -964,12 +972,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -985,17 +993,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>175</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="R6" t="n">
-        <v>256</v>
+        <v>14</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1004,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1575783414</t>
+          <t>1506954140</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1575783414</t>
+          <t>https://m.place.naver.com/place/1506954140</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1026,34 +1034,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>레디PT 피티샵</t>
+          <t>컴온짐</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>phil2jh@naver.com</t>
+          <t>comeon2525@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1403-0083</t>
+          <t>054-474-6262</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 석적읍 남율로2길 1 3층</t>
+          <t>경상북도 구미시 인동가산로 23 지하1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_ready_pt.studio?igsh=MXhseW92Y3N0cHNqcA==</t>
+          <t>https://m.cafe.naver.com/machogym</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1079,17 +1087,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R7" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1098,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1760644933</t>
+          <t>1914240718</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1760644933</t>
+          <t>https://m.place.naver.com/place/1914240718</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1120,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>아이엔짐</t>
+          <t>온리원피트니스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ingym_ho@naver.com</t>
+          <t>onlyone_pt@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>070-4101-4354</t>
+          <t>0507-1405-6622</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동중앙로1길 18 2,3층 아이엔짐</t>
+          <t>경상북도 구미시 인동가산로 35 3층, 4층, 5층 온리원 피트니스</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://blog.naver.com/ingym_ho</t>
+          <t>https://blog.naver.com/onlyone_pt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1168,7 +1176,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1177,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>87</v>
+        <v>311</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>130</v>
       </c>
       <c r="R8" t="n">
-        <v>93</v>
+        <v>441</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1065996176</t>
+          <t>15864016</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1065996176</t>
+          <t>https://m.place.naver.com/place/15864016</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1214,29 +1222,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>365피트니스 헬스 PT</t>
+          <t>인동스피닝</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gkgkghgh234@naver.com</t>
+          <t>lee71002091@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>054-716-2340</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산호대로29길 8-3 301호</t>
+          <t>경상북도 구미시 인동중앙로 16 4층 인동스피닝</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/365_fitness24</t>
+          <t>https://cafe.naver.com/a0139</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1251,7 +1255,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1267,17 +1271,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>73</v>
+        <v>3</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,17 +1290,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1111348451</t>
+          <t>37841949</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1111348451</t>
+          <t>https://m.place.naver.com/place/37841949</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1308,29 +1312,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>존킴짐</t>
+          <t>케이투휘트니스헬스클럽</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>johnkimgym@naver.com</t>
+          <t>topten0@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1367-1260</t>
+          <t>0507-1403-7552</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로2길 15 바젤2차 606호</t>
+          <t>경상북도 구미시 인동26길 43-4 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/johnkimgym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1340,12 +1344,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1365,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,46 +1384,46 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1103689398</t>
+          <t>1903697781</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1103689398</t>
+          <t>https://m.place.naver.com/place/1903697781</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>목욕탕,사우나</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>하더짐</t>
+          <t>천호사우나헬스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>qkek630@naver.com</t>
+          <t>isis0328@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1800-9978</t>
+          <t>054-977-5440</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동중앙로6길 1 3층</t>
+          <t>경상북도 칠곡군 석적읍 북중리11길 23</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1459,13 +1463,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="Q11" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="R11" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,17 +1478,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1197601467</t>
+          <t>15510481</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1197601467</t>
+          <t>https://m.place.naver.com/place/15510481</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1496,44 +1500,44 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Life fitness</t>
+          <t>스타헬스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>starrude@naver.com</t>
+          <t>147048@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1316-4806</t>
+          <t>054-475-1383</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동31길 22-17 4층</t>
+          <t>경상북도 구미시 흥안로 18</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>http://instagram.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1549,17 +1553,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,17 +1572,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1788318048</t>
+          <t>15523431</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1788318048</t>
+          <t>https://m.place.naver.com/place/15523431</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1590,38 +1594,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>엠투피 산동점</t>
+          <t>에스엘짐</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>m2plove@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>m2plove@m2p.co.kr</t>
-        </is>
-      </c>
+          <t>tankboy486@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1314-3508</t>
+          <t>0507-1379-0910</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당2로 57</t>
+          <t>경상북도 구미시 검성로 103-7 화진금봉 1차 상가 B1</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>http://www.m2p.co.kr</t>
+          <t>https://blog.naver.com/tankboy486</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1647,17 +1647,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>260</v>
+        <v>54</v>
       </c>
       <c r="Q13" t="n">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="R13" t="n">
-        <v>349</v>
+        <v>79</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1666,17 +1666,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1373982303</t>
+          <t>1798303624</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1373982303</t>
+          <t>https://m.place.naver.com/place/1798303624</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1688,34 +1688,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>컴온짐</t>
+          <t>바디엔지니어스짐 산동점</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>comeon2525@naver.com</t>
+          <t>bodybody01@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>054-474-6262</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동가산로 23 지하1층</t>
+          <t>경상북도 구미시 산동읍 신당1로4길 3 에코빌딩 5,6층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://m.cafe.naver.com/machogym</t>
+          <t>https://www.instagram.com/bodyengineersgym_sandong</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1736,22 +1732,22 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="Q14" t="n">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="R14" t="n">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1760,17 +1756,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1914240718</t>
+          <t>1046159743</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1914240718</t>
+          <t>https://m.place.naver.com/place/1046159743</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1782,29 +1778,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>휘트니스인앤아웃</t>
+          <t>피트니스G 헬스.PT 석적점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ouihun@naver.com</t>
+          <t>fitnessg4422229@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>054-473-9488</t>
+          <t>054-972-2229</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 적림1길 7-3</t>
+          <t>경상북도 칠곡군 석적읍 유학로 1 401호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>http://blog.naver.com/ouihun</t>
+          <t>https://www.instagram.com/fitness.g_02</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1819,7 +1815,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1835,17 +1831,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3</v>
+        <v>132</v>
       </c>
       <c r="Q15" t="n">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="R15" t="n">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1854,17 +1850,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>37765614</t>
+          <t>1530354048</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37765614</t>
+          <t>https://m.place.naver.com/place/1530354048</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1876,29 +1872,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>파워헬스클럽</t>
+          <t>아이엔짐</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>power2963805@naver.com</t>
+          <t>ingym_ho@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1433-7656</t>
+          <t>070-4101-4354</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산호대로27길 14 2층</t>
+          <t>경상북도 구미시 인동중앙로1길 18 2,3층 아이엔짐</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://blog.naver.com/ingym_ho</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1908,12 +1904,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1929,17 +1925,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R16" t="n">
-        <v>4</v>
+        <v>93</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1948,17 +1944,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1197556873</t>
+          <t>1065996176</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1197556873</t>
+          <t>https://m.place.naver.com/place/1065996176</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1970,25 +1966,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>인동스피닝</t>
+          <t>인동스포렉스</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>lee71002091@naver.com</t>
+          <t>nunmur0604@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>054-472-7161</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동중앙로 16 4층 인동스피닝</t>
+          <t>경상북도 구미시 인동중앙로 23-3</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://cafe.naver.com/a0139</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2026,10 +2026,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2038,17 +2038,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>37841949</t>
+          <t>21799533</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37841949</t>
+          <t>https://m.place.naver.com/place/21799533</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2060,25 +2060,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>네오젠 골프컨디셔닝 스튜디오</t>
+          <t>짐다이나믹</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>hangsangharu@naver.com</t>
+          <t>ckdsha77@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1319-1733</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동36길 71</t>
+          <t>경상북도 구미시 인동중앙로3길 14 인동프라자 202호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/gym_dynamic</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2088,7 +2092,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2109,17 +2113,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2128,17 +2132,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1986933515</t>
+          <t>1756168748</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1986933515</t>
+          <t>https://m.place.naver.com/place/1756168748</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2150,25 +2154,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>티나핏</t>
+          <t>구미스포츠월드</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>loveseung22@naver.com</t>
+          <t>gbnadri@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>054-471-8965</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 석적읍 장곡길 119 중앙빌딩 4층</t>
+          <t>경상북도 구미시 인동35길 32</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tina_fit__</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2178,7 +2186,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2199,17 +2207,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P19" t="n">
+        <v>108</v>
+      </c>
+      <c r="Q19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>267</v>
-      </c>
       <c r="R19" t="n">
-        <v>267</v>
+        <v>108</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2218,17 +2226,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1940941739</t>
+          <t>1573436640</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1940941739</t>
+          <t>https://m.place.naver.com/place/1573436640</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2240,29 +2248,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>XO 피트니스 24시</t>
+          <t>점핑피트니스</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>gg123455@naver.com</t>
+          <t>chlgpwjd19@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1374-6544</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동북길 83 5,6층</t>
+          <t>경상북도 구미시 인동38길 9-8 종합프라자</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://youtube.com/channel/UC5g0GbfBdaQPl5t3gt1mzLw?si=Vo3FSmjrAXF9KdW4</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2272,7 +2276,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2293,17 +2297,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2312,17 +2316,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1951938661</t>
+          <t>1293494349</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1951938661</t>
+          <t>https://m.place.naver.com/place/1293494349</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2334,29 +2338,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>웰라인 휘트니스</t>
+          <t>커브스 구평클럽</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>topten0@naver.com</t>
+          <t>mik6158@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>054-473-7227</t>
+          <t>054-476-1330</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동가산로 9-3 노블레스타워 8층 웰라인휘트니스</t>
+          <t>경상북도 구미시 인동36길 15 구평메디컬센터 6층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/mik6158</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2366,12 +2370,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2391,13 +2395,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="Q21" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2406,17 +2410,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1506954140</t>
+          <t>20460818</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1506954140</t>
+          <t>https://m.place.naver.com/place/20460818</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2428,38 +2432,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>엠투피 구평점</t>
+          <t>제이디짐 산동점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>m2plove@naver.com</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>m2plove@m2p.co.kr</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0507-1358-9689</t>
-        </is>
-      </c>
+          <t>jdgym6606@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동38길 5-9</t>
+          <t>경상북도 구미시 산동읍 신당1로4길 19 3층 제이디짐</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>http://www.m2p.co.kr</t>
+          <t>https://blog.naver.com/jdgym6606</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2489,13 +2485,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>373</v>
+        <v>175</v>
       </c>
       <c r="Q22" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="R22" t="n">
-        <v>438</v>
+        <v>256</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2504,17 +2500,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1735292694</t>
+          <t>1575783414</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1735292694</t>
+          <t>https://m.place.naver.com/place/1575783414</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2526,34 +2522,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>커브스 구평클럽</t>
+          <t>Life fitness</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>mik6158@naver.com</t>
+          <t>starrude@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>054-476-1330</t>
+          <t>0507-1316-4806</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동36길 15 구평메디컬센터 6층</t>
+          <t>경상북도 구미시 인동31길 22-17 4층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mik6158</t>
+          <t>http://instagram.com/</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2579,17 +2575,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2598,17 +2594,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>20460818</t>
+          <t>1788318048</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20460818</t>
+          <t>https://m.place.naver.com/place/1788318048</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2620,29 +2616,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>인동스포렉스</t>
+          <t>로드핏 구평점 헬스 PT</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>nunmur0604@naver.com</t>
+          <t>lordfit@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>054-472-7161</t>
+          <t>0507-1364-3750</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동중앙로 23-3</t>
+          <t>경상북도 구미시 인동남길 178 6층, 7층, 8층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lordfit_gupyeong</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2652,7 +2648,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2673,17 +2669,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2692,17 +2688,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>21799533</t>
+          <t>2082865295</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21799533</t>
+          <t>https://m.place.naver.com/place/2082865295</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2714,29 +2710,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>크로스핏매니악</t>
+          <t>피트니스247</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>minhuisu@naver.com</t>
+          <t>seop__e@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>054-471-7279</t>
+          <t>0507-1399-2471</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계북로 36 옥계메디칼타워 지하2층</t>
+          <t>경상북도 구미시 인동중앙로11길 26 3층 피트니스247</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/crossfitmaniac</t>
+          <t>https://www.instagram.com/fitness247_gumi/</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2771,13 +2767,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3</v>
+        <v>418</v>
       </c>
       <c r="Q25" t="n">
-        <v>114</v>
+        <v>267</v>
       </c>
       <c r="R25" t="n">
-        <v>117</v>
+        <v>685</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2786,17 +2782,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>36420484</t>
+          <t>1579467156</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36420484</t>
+          <t>https://m.place.naver.com/place/1579467156</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2808,29 +2804,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>로드핏 구평점 헬스 PT</t>
+          <t>팀JJ피트니스 옥계점</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>lordfit@naver.com</t>
+          <t>teamjj0626@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1364-3750</t>
+          <t>0507-1486-8853</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동남길 178 6층, 7층, 8층</t>
+          <t>경상북도 구미시 옥계북로 22 7층, 6층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lordfit_gupyeong</t>
+          <t>https://blog.naver.com/teamjj0626</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2845,7 +2841,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2865,13 +2861,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>160</v>
+        <v>1966</v>
       </c>
       <c r="Q26" t="n">
-        <v>111</v>
+        <v>325</v>
       </c>
       <c r="R26" t="n">
-        <v>271</v>
+        <v>2291</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2880,17 +2876,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>2082865295</t>
+          <t>1389388394</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2082865295</t>
+          <t>https://m.place.naver.com/place/1389388394</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2902,24 +2898,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>스타헬스</t>
+          <t>네오젠 골프컨디셔닝 스튜디오</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>147048@naver.com</t>
+          <t>hangsangharu@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>054-475-1383</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경상북도 구미시 흥안로 18</t>
+          <t>경상북도 구미시 인동36길 71</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2959,13 +2951,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2974,17 +2966,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>15523431</t>
+          <t>1986933515</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/15523431</t>
+          <t>https://m.place.naver.com/place/1986933515</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -2996,25 +2988,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>점핑피트니스</t>
+          <t>구미필라테스</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>chlgpwjd19@naver.com</t>
+          <t>pmhcrow@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>054-475-4477</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동38길 9-8 종합프라자</t>
+          <t>경상북도 구미시 인동36길 6 5층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/pmhcrow</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3024,12 +3020,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3049,13 +3045,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="R28" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3064,17 +3060,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1293494349</t>
+          <t>19460024</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1293494349</t>
+          <t>https://m.place.naver.com/place/19460024</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3086,29 +3082,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>케이투휘트니스헬스클럽</t>
+          <t>XO 피트니스 24시</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>topten0@naver.com</t>
+          <t>gg123455@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1403-7552</t>
+          <t>0507-1374-6544</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동26길 43-4 4층</t>
+          <t>경상북도 구미시 인동북길 83 5,6층</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/channel/UC5g0GbfBdaQPl5t3gt1mzLw?si=Vo3FSmjrAXF9KdW4</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3118,7 +3114,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3139,17 +3135,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="R29" t="n">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3158,17 +3154,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1903697781</t>
+          <t>1951938661</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1903697781</t>
+          <t>https://m.place.naver.com/place/1951938661</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3180,29 +3176,25 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>팀JJ피트니스 석적점</t>
+          <t>PT LAB.피트니스</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>teamjj0626@naver.com</t>
+          <t>ptlab21@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0507-1392-9101</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 석적읍 유학로 12 3,4층</t>
+          <t>경상북도 구미시 옥계북로 34 원광빌딩, 4층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ptlab21</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3212,12 +3204,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3228,22 +3220,22 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="Q30" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3252,17 +3244,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1501991558</t>
+          <t>1255504991</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1501991558</t>
+          <t>https://m.place.naver.com/place/1255504991</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3274,24 +3266,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>구미스포츠월드</t>
+          <t>아이엠헬스&amp;휘트니스</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>gbnadri@naver.com</t>
+          <t>imtotal@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>054-471-8965</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동35길 32</t>
+          <t>경상북도 칠곡군 석적읍 북중리11길 23</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3331,13 +3319,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3346,51 +3334,51 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1573436640</t>
+          <t>15510473</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1573436640</t>
+          <t>https://m.place.naver.com/place/15510473</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>목욕탕,사우나</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>천호사우나헬스</t>
+          <t>크로스핏매니악</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>isis0328@naver.com</t>
+          <t>minhuisu@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>054-977-5440</t>
+          <t>054-471-7279</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 석적읍 북중리11길 23</t>
+          <t>경상북도 구미시 옥계북로 36 옥계메디칼타워 지하2층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/crossfitmaniac</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3400,7 +3388,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3421,17 +3409,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="Q32" t="n">
-        <v>6</v>
+        <v>114</v>
       </c>
       <c r="R32" t="n">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3440,17 +3428,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>15510481</t>
+          <t>36420484</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/15510481</t>
+          <t>https://m.place.naver.com/place/36420484</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3462,29 +3450,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>피트니스247</t>
+          <t>파워헬스클럽</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>seop__e@naver.com</t>
+          <t>power2963805@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1399-2471</t>
+          <t>0507-1433-7656</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동중앙로11길 26 3층 피트니스247</t>
+          <t>경상북도 구미시 산호대로27길 14 2층</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fitness247_gumi/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3494,7 +3482,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3515,17 +3503,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>417</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>267</v>
+        <v>4</v>
       </c>
       <c r="R33" t="n">
-        <v>684</v>
+        <v>4</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3534,17 +3522,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1579467156</t>
+          <t>1197556873</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1579467156</t>
+          <t>https://m.place.naver.com/place/1197556873</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3556,29 +3544,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>피트니스G 헬스.PT 석적점</t>
+          <t>티나핏</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>fitnessg4422229@naver.com</t>
+          <t>loveseung22@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>054-972-2229</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 석적읍 유학로 1 401호</t>
+          <t>경상북도 칠곡군 석적읍 장곡길 119 중앙빌딩 4층</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/fitness.g_02</t>
+          <t>https://www.instagram.com/tina_fit__</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3613,13 +3597,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>37</v>
+        <v>267</v>
       </c>
       <c r="R34" t="n">
-        <v>169</v>
+        <v>267</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3628,17 +3612,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1530354048</t>
+          <t>1940941739</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1530354048</t>
+          <t>https://m.place.naver.com/place/1940941739</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3650,29 +3634,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>구미필라테스</t>
+          <t>레디PT 피티샵</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>pmhcrow@naver.com</t>
+          <t>phil2jh@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>054-475-4477</t>
+          <t>0507-1403-0083</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동36길 6 5층</t>
+          <t>경상북도 칠곡군 석적읍 남율로2길 1 3층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pmhcrow</t>
+          <t>https://www.instagram.com/_ready_pt.studio?igsh=MXhseW92Y3N0cHNqcA==</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3687,7 +3671,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3703,17 +3687,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="R35" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3722,17 +3706,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>19460024</t>
+          <t>1760644933</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19460024</t>
+          <t>https://m.place.naver.com/place/1760644933</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3744,29 +3728,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>최재원피트니스 구미인동점</t>
+          <t>365피트니스 헬스 PT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>energy1262@naver.com</t>
+          <t>gkgkghgh234@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1439-9698</t>
+          <t>054-716-2340</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동북길 43 4F</t>
+          <t>경상북도 구미시 산호대로29길 8-3 301호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/choijaewonfitness</t>
+          <t>https://www.instagram.com/365_fitness24</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3801,13 +3785,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="Q36" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="R36" t="n">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3816,17 +3800,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1971423118</t>
+          <t>1111348451</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1971423118</t>
+          <t>https://m.place.naver.com/place/1111348451</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3838,25 +3822,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>아이엠헬스&amp;휘트니스</t>
+          <t>존킴짐</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>imtotal@naver.com</t>
+          <t>johnkimgym@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1367-1260</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 석적읍 북중리11길 23</t>
+          <t>경상북도 구미시 산동읍 신당1로2길 15 바젤2차 606호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/johnkimgym</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3866,12 +3854,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3891,13 +3879,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3906,17 +3894,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>15510473</t>
+          <t>1103689398</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/15510473</t>
+          <t>https://m.place.naver.com/place/1103689398</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -3928,29 +3916,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>에스엘짐</t>
+          <t>엠투피 구평점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>tankboy486@naver.com</t>
+          <t>m2plove@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1379-0910</t>
+          <t>0507-1358-9689</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경상북도 구미시 검성로 103-7 화진금봉 1차 상가 B1</t>
+          <t>경상북도 구미시 인동38길 5-9</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tankboy486</t>
+          <t>http://www.m2p.co.kr</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3965,7 +3953,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3981,17 +3969,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>54</v>
+        <v>373</v>
       </c>
       <c r="Q38" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="R38" t="n">
-        <v>79</v>
+        <v>438</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4000,17 +3988,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1798303624</t>
+          <t>1735292694</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1798303624</t>
+          <t>https://m.place.naver.com/place/1735292694</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4022,25 +4010,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>바디엔지니어스짐 산동점</t>
+          <t>엠투피 산동점</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>bodybody01@naver.com</t>
+          <t>m2plove@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1314-3508</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로4길 3 에코빌딩 5,6층</t>
+          <t>경상북도 구미시 산동읍 신당2로 57</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bodyengineersgym_sandong</t>
+          <t>http://www.m2p.co.kr</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4066,7 +4058,7 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4075,13 +4067,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>57</v>
+        <v>260</v>
       </c>
       <c r="Q39" t="n">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="R39" t="n">
-        <v>123</v>
+        <v>349</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4090,17 +4082,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1046159743</t>
+          <t>1373982303</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1046159743</t>
+          <t>https://m.place.naver.com/place/1373982303</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4194,7 +4186,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4280,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4300,34 +4292,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>토미짐앤스파</t>
+          <t>클락짐_Clark Gym</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>tomigym@naver.com</t>
+          <t>sungminjin1004@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>054-471-8964</t>
+          <t>0507-1359-2673</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동35길 32 토미짐앤스파</t>
+          <t>경상북도 칠곡군 석적읍 북중리10길 26 2층(가람타운)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tomigym</t>
+          <t>https://www.facebook.com/kyunghoonji</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4357,13 +4349,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>106</v>
+        <v>15</v>
       </c>
       <c r="Q42" t="n">
-        <v>160</v>
+        <v>5</v>
       </c>
       <c r="R42" t="n">
-        <v>266</v>
+        <v>20</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4372,17 +4364,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>38257162</t>
+          <t>1032303624</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38257162</t>
+          <t>https://m.place.naver.com/place/1032303624</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4464,7 @@
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4484,25 +4476,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>우먼앤짐</t>
+          <t>팀레이피트니스 진평1호점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>woman_and_gym@naver.com</t>
+          <t>nyunyu@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1313-3551</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당1로2길 13 1동 206호(바젤메디컬프라자)</t>
+          <t>경상북도 구미시 인동22길 19 4층 팀레이 피트니스</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/woman_and_gym_gumi_pt/</t>
+          <t>https://www.instagram.com/teamray_1st</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4537,13 +4533,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="Q44" t="n">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="R44" t="n">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4552,17 +4548,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1934228891</t>
+          <t>1235167357</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1934228891</t>
+          <t>https://m.place.naver.com/place/1235167357</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4574,29 +4570,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>제이원 스파랜드 구미점</t>
+          <t>짐케이 PT</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>sukja7820@naver.com</t>
+          <t>a319314@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>054-471-0011</t>
+          <t>0507-1393-9683</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 강동로 1159-57</t>
+          <t>경상북도 구미시 산동읍 신당2로 29 6층</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jone.gumi?igsh=N2l3OTR0MGIyem00&amp;utm_source=ig_contact_invite</t>
+          <t>https://blog.naver.com/a319314</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4611,7 +4607,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4627,17 +4623,17 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="Q45" t="n">
-        <v>53</v>
+        <v>179</v>
       </c>
       <c r="R45" t="n">
-        <v>201</v>
+        <v>252</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4646,17 +4642,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1187212013</t>
+          <t>1055349957</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1187212013</t>
+          <t>https://m.place.naver.com/place/1055349957</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4668,29 +4664,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>이루핏</t>
+          <t>루시피트니스</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>papepopo0929@naver.com</t>
+          <t>lucy_fitness@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1353-8028</t>
+          <t>0507-1395-4181</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>경상북도 구미시 옥계북로10길 4 2층</t>
+          <t>경상북도 구미시 산호대로29길 9 2층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lucyfitness_gumi</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4700,7 +4696,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4721,17 +4717,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="Q46" t="n">
-        <v>320</v>
+        <v>3</v>
       </c>
       <c r="R46" t="n">
-        <v>322</v>
+        <v>45</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4740,17 +4736,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1399469071</t>
+          <t>1426804590</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1399469071</t>
+          <t>https://m.place.naver.com/place/1426804590</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4762,25 +4758,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>피티타임/PT</t>
+          <t>율핏</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>shs8461@naver.com</t>
+          <t>jueun931022@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1382-1537</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 석적읍 북중리12길 19 ,2층</t>
+          <t>경상북도 구미시 인동중앙로1길 1 2층 율핏</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/shs8461</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4811,17 +4811,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="R47" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4830,17 +4830,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1168516436</t>
+          <t>1395755565</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1168516436</t>
+          <t>https://m.place.naver.com/place/1395755565</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4852,34 +4852,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>클락짐_Clark Gym</t>
+          <t>지와이피티샵</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>sungminjin1004@naver.com</t>
+          <t>topten0@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1359-2673</t>
+          <t>0507-1365-8610</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>경상북도 칠곡군 석적읍 북중리10길 26 2층(가람타운)</t>
+          <t>대구광역시 군위군 군위읍 중앙길 72 2층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/kyunghoonji</t>
+          <t>https://www.instagram.com/gypt86</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4909,13 +4909,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Q48" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R48" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4924,17 +4924,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1032303624</t>
+          <t>1756594082</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1032303624</t>
+          <t>https://m.place.naver.com/place/1756594082</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -4946,29 +4946,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>쇠타작PT</t>
+          <t>이루핏</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1288xo@naver.com</t>
+          <t>papepopo0929@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1346-6290</t>
+          <t>0507-1353-8028</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당인덕1로3길 3 4층</t>
+          <t>경상북도 구미시 옥계북로10길 4 2층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/1288xo</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4978,12 +4978,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4994,7 +4994,7 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -5003,13 +5003,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="Q49" t="n">
-        <v>16</v>
+        <v>320</v>
       </c>
       <c r="R49" t="n">
-        <v>38</v>
+        <v>322</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5018,17 +5018,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1393651171</t>
+          <t>1399469071</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1393651171</t>
+          <t>https://m.place.naver.com/place/1399469071</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5040,29 +5040,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>짐케이 PT</t>
+          <t>헤이핏</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>a319314@naver.com</t>
+          <t>hyelin0716@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0507-1393-9683</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당2로 29 6층</t>
+          <t>경상북도 구미시 산동읍 신당4로 115 1동 7F 701호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/a319314</t>
+          <t>https://www.instagram.com/__heyfit</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5077,7 +5073,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5093,17 +5089,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="Q50" t="n">
-        <v>179</v>
+        <v>231</v>
       </c>
       <c r="R50" t="n">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5112,17 +5108,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1055349957</t>
+          <t>1584468732</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1055349957</t>
+          <t>https://m.place.naver.com/place/1584468732</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5134,29 +5130,25 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>지와이피티샵</t>
+          <t>우먼앤짐</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>topten0@naver.com</t>
+          <t>woman_and_gym@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0507-1365-8610</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>대구광역시 군위군 군위읍 중앙길 72 2층</t>
+          <t>경상북도 구미시 산동읍 신당1로2길 13 1동 206호(바젤메디컬프라자)</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gypt86</t>
+          <t>https://www.instagram.com/woman_and_gym_gumi_pt/</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5191,13 +5183,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="Q51" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R51" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5206,17 +5198,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1756594082</t>
+          <t>1934228891</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1756594082</t>
+          <t>https://m.place.naver.com/place/1934228891</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5302,7 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5322,29 +5314,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>루시피트니스</t>
+          <t>제이원 스파랜드 구미점</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>lucy_fitness@naver.com</t>
+          <t>jewel2248@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1395-4181</t>
+          <t>054-471-0011</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산호대로29길 9 2층</t>
+          <t>경상북도 구미시 산동읍 강동로 1159-57</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lucyfitness_gumi</t>
+          <t>https://www.instagram.com/jone.gumi?igsh=N2l3OTR0MGIyem00&amp;utm_source=ig_contact_invite</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5379,13 +5371,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>42</v>
+        <v>148</v>
       </c>
       <c r="Q53" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="R53" t="n">
-        <v>45</v>
+        <v>201</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5394,17 +5386,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1426804590</t>
+          <t>1187212013</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1426804590</t>
+          <t>https://m.place.naver.com/place/1187212013</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5416,29 +5408,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>팀레이피트니스 진평1호점</t>
+          <t>토미짐앤스파</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>nyunyu@naver.com</t>
+          <t>tomigym@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1313-3551</t>
+          <t>054-471-8964</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동22길 19 4층 팀레이 피트니스</t>
+          <t>경상북도 구미시 인동35길 32 토미짐앤스파</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/teamray_1st</t>
+          <t>https://blog.naver.com/tomigym</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5453,7 +5445,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5473,13 +5465,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>4</v>
+        <v>106</v>
       </c>
       <c r="Q54" t="n">
-        <v>91</v>
+        <v>160</v>
       </c>
       <c r="R54" t="n">
-        <v>95</v>
+        <v>266</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5488,17 +5480,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1235167357</t>
+          <t>38257162</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1235167357</t>
+          <t>https://m.place.naver.com/place/38257162</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5510,29 +5502,25 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>율핏</t>
+          <t>피티타임/PT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>jueun931022@naver.com</t>
+          <t>shs8461@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>0507-1382-1537</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>경상북도 구미시 인동중앙로1길 1 2층 율핏</t>
+          <t>경상북도 칠곡군 석적읍 북중리12길 19 ,2층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/shs8461</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5542,12 +5530,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5563,17 +5551,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="Q55" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="R55" t="n">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5582,17 +5570,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1395755565</t>
+          <t>1168516436</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1395755565</t>
+          <t>https://m.place.naver.com/place/1168516436</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5604,25 +5592,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>헤이핏</t>
+          <t>쇠타작PT</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>hyelin0716@naver.com</t>
+          <t>1288xo@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1346-6290</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>경상북도 구미시 산동읍 신당4로 115 1동 7F 701호</t>
+          <t>경상북도 구미시 산동읍 신당인덕1로3길 3 4층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/__heyfit</t>
+          <t>https://blog.naver.com/1288xo</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5637,7 +5629,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5648,22 +5640,22 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q56" t="n">
-        <v>230</v>
+        <v>16</v>
       </c>
       <c r="R56" t="n">
-        <v>249</v>
+        <v>38</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5672,17 +5664,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1584468732</t>
+          <t>1393651171</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1584468732</t>
+          <t>https://m.place.naver.com/place/1393651171</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5768,7 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -5870,7 +5862,7 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
